--- a/projectFor3Lab/New_Table3.xlsx
+++ b/projectFor3Lab/New_Table3.xlsx
@@ -111,19 +111,19 @@
         <v>5</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>398.0</v>
+        <v>508.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>546.0</v>
+        <v>552.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>158.0</v>
+        <v>86.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1687.0</v>
+        <v>1949.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>88.0</v>
+        <v>112.0</v>
       </c>
     </row>
     <row r="4">
@@ -131,19 +131,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>636.0</v>
+        <v>848.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>546.0</v>
+        <v>552.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>90.0</v>
+        <v>103.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>1814.0</v>
+        <v>2143.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>64.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="5">
@@ -151,19 +151,19 @@
         <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>1110.0</v>
+        <v>1321.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>546.0</v>
+        <v>552.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>118.0</v>
+        <v>153.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>1893.0</v>
+        <v>1897.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>62.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="6">
@@ -171,19 +171,19 @@
         <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>2099.0</v>
+        <v>2738.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>546.0</v>
+        <v>552.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>164.0</v>
+        <v>182.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>1768.0</v>
+        <v>2086.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>165.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="7">
@@ -191,19 +191,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>3267.0</v>
+        <v>3067.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>546.0</v>
+        <v>552.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>196.0</v>
+        <v>223.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>2047.0</v>
+        <v>2241.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>175.0</v>
+        <v>87.0</v>
       </c>
     </row>
   </sheetData>

--- a/projectFor3Lab/New_Table3.xlsx
+++ b/projectFor3Lab/New_Table3.xlsx
@@ -111,19 +111,19 @@
         <v>5</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>508.0</v>
+        <v>607.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>552.0</v>
+        <v>700.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>86.0</v>
+        <v>97.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1949.0</v>
+        <v>1769.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>112.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="4">
@@ -131,19 +131,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>848.0</v>
+        <v>878.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>552.0</v>
+        <v>700.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>103.0</v>
+        <v>118.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>2143.0</v>
+        <v>1992.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>79.0</v>
+        <v>174.0</v>
       </c>
     </row>
     <row r="5">
@@ -151,19 +151,19 @@
         <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>1321.0</v>
+        <v>1491.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>552.0</v>
+        <v>700.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>153.0</v>
+        <v>220.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>1897.0</v>
+        <v>1389.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>70.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="6">
@@ -171,19 +171,19 @@
         <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>2738.0</v>
+        <v>3100.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>552.0</v>
+        <v>700.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>182.0</v>
+        <v>227.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>2086.0</v>
+        <v>1642.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>87.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="7">
@@ -191,19 +191,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>3067.0</v>
+        <v>3266.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>552.0</v>
+        <v>700.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>223.0</v>
+        <v>257.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>2241.0</v>
+        <v>1815.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>87.0</v>
+        <v>82.0</v>
       </c>
     </row>
   </sheetData>
